--- a/output_tcc_var/tabelas/testes_estacionariedade_log_e_dlog.xlsx
+++ b/output_tcc_var/tabelas/testes_estacionariedade_log_e_dlog.xlsx
@@ -478,19 +478,19 @@
         <v>273</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.261148021653276</v>
+        <v>-3.261267467308059</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07289118378502206</v>
+        <v>0.07286998927143015</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1395863617619791</v>
+        <v>0.1395699318446345</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06187710784818687</v>
+        <v>0.06190753362104719</v>
       </c>
       <c r="I2" t="n">
         <v>10</v>
@@ -511,16 +511,16 @@
         <v>272</v>
       </c>
       <c r="D3" t="n">
-        <v>-9.16148881719954</v>
+        <v>-9.1608482558249</v>
       </c>
       <c r="E3" t="n">
-        <v>2.525998119494847e-15</v>
+        <v>2.535534548201614e-15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07402020481070469</v>
+        <v>0.0740392962638512</v>
       </c>
       <c r="H3" t="n">
         <v>0.1</v>
@@ -742,16 +742,16 @@
         <v>273</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.592928607535553</v>
+        <v>-2.592928607535574</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2831583181249443</v>
+        <v>0.2831583181249339</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3597047451300194</v>
+        <v>0.3597047451300509</v>
       </c>
       <c r="H10" t="n">
         <v>0.01</v>
@@ -775,16 +775,16 @@
         <v>272</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.34111106642188</v>
+        <v>-10.34111106642193</v>
       </c>
       <c r="E11" t="n">
-        <v>2.683750516909036e-18</v>
+        <v>2.683750516908304e-18</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05752518686680646</v>
+        <v>0.05752518686680586</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
@@ -808,16 +808,16 @@
         <v>273</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.195942824564393</v>
+        <v>-3.145098199633721</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08521318126661853</v>
+        <v>0.09590687878706183</v>
       </c>
       <c r="F12" t="n">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.114986798523424</v>
+        <v>0.09565682460805554</v>
       </c>
       <c r="H12" t="n">
         <v>0.1</v>
@@ -841,16 +841,16 @@
         <v>272</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.516478530555672</v>
+        <v>-5.934577571025955</v>
       </c>
       <c r="E13" t="n">
-        <v>0.007573839528066595</v>
+        <v>2.337296381646106e-07</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1625926205915499</v>
+        <v>0.1953889698382997</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
@@ -874,16 +874,16 @@
         <v>273</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.289489474793716</v>
+        <v>-3.28948947479372</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06799849004639813</v>
+        <v>0.06799849004639745</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3605323732778131</v>
+        <v>0.360532373277808</v>
       </c>
       <c r="H14" t="n">
         <v>0.01</v>
@@ -907,16 +907,16 @@
         <v>272</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.927820503168507</v>
+        <v>-9.927820503168487</v>
       </c>
       <c r="E15" t="n">
-        <v>2.875531303303065e-17</v>
+        <v>2.875531303303437e-17</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05681786464756745</v>
+        <v>0.05681786464756759</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
@@ -940,16 +940,16 @@
         <v>273</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.412894199912437</v>
+        <v>-5.412894199912431</v>
       </c>
       <c r="E16" t="n">
-        <v>3.417298779312811e-05</v>
+        <v>3.41729877931292e-05</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0978346985657447</v>
+        <v>0.09783469856574682</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
@@ -973,16 +973,16 @@
         <v>272</v>
       </c>
       <c r="D17" t="n">
-        <v>-8.251558048056454</v>
+        <v>-8.251558048056459</v>
       </c>
       <c r="E17" t="n">
-        <v>5.373779515846288e-13</v>
+        <v>5.373779515846092e-13</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02508959284530602</v>
+        <v>0.02508959284530604</v>
       </c>
       <c r="H17" t="n">
         <v>0.1</v>
@@ -1006,16 +1006,16 @@
         <v>273</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.509089620490692</v>
+        <v>-2.509089620490691</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3234328158719428</v>
+        <v>0.3234328158719435</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3728105910265165</v>
+        <v>0.372810591026517</v>
       </c>
       <c r="H18" t="n">
         <v>0.01</v>
@@ -1039,16 +1039,16 @@
         <v>272</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.785477784097127</v>
+        <v>-6.78547778409713</v>
       </c>
       <c r="E19" t="n">
-        <v>2.438402753734057e-09</v>
+        <v>2.438402753734004e-09</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.09366789288757732</v>
+        <v>0.09366789288757728</v>
       </c>
       <c r="H19" t="n">
         <v>0.1</v>
